--- a/tame_output/ON/bt/strategyON_20231022.xlsx
+++ b/tame_output/ON/bt/strategyON_20231022.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.0%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>100.8%</t>
+          <t>100.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.1%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.9%</t>
+          <t>-157.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.3%</t>
+          <t>130.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.03</t>
+          <t>4.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-10-20</t>
+          <t>2023-10-21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.7%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1757"/>
+  <dimension ref="A1:G1758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -41921,7 +41921,7 @@
         <v>45219</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.900622812205591</v>
+        <v>2.902669647939156</v>
       </c>
       <c r="C1757" t="n">
         <v>2.968547780644436</v>
@@ -41937,6 +41937,29 @@
       </c>
       <c r="G1757" t="n">
         <v>4.267128375135563</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="2" t="n">
+        <v>45220</v>
+      </c>
+      <c r="B1758" t="n">
+        <v>2.911674046606653</v>
+      </c>
+      <c r="C1758" t="n">
+        <v>2.965146865274802</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>1.577166789527658</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>3.595657156772119</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>2.164300990818542</v>
+      </c>
+      <c r="G1758" t="n">
+        <v>4.26372745976593</v>
       </c>
     </row>
   </sheetData>
